--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T10:23:38+00:00</t>
+    <t>2025-02-24T13:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:55:23+00:00</t>
+    <t>2025-02-26T08:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T08:56:44+00:00</t>
+    <t>2025-03-04T11:06:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T11:06:18+00:00</t>
+    <t>2025-03-06T12:24:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T12:24:43+00:00</t>
+    <t>2025-03-20T12:28:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T12:28:15+00:00</t>
+    <t>2025-03-24T06:28:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
@@ -26,7 +26,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/ValueSet/at-aps-observationinterpretation</t>
+    <t>https://fhir.hl7.at/elga/aps/r4/ValueSet/at-aps-observationinterpretation</t>
   </si>
   <si>
     <t>Version</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T06:28:05+00:00</t>
+    <t>2025-03-24T07:27:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T07:27:46+00:00</t>
+    <t>2025-03-24T07:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-18T10:23:29+00:00</t>
+    <t>2026-01-28T10:05:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T10:05:57+00:00</t>
+    <t>2026-01-29T06:33:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T06:33:09+00:00</t>
+    <t>2026-02-03T10:06:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:06:44+00:00</t>
+    <t>2026-02-03T10:34:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-observationinterpretation.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:34:36+00:00</t>
+    <t>2026-02-09T07:50:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
